--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2462"/>
+  <dimension ref="A1:F2463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49652,19 +49652,39 @@
         <v>46276</v>
       </c>
       <c r="B2462" t="n">
-        <v>193.1</v>
+        <v>193.1000061035156</v>
       </c>
       <c r="C2462" t="n">
         <v>194.5</v>
       </c>
       <c r="D2462" t="n">
-        <v>192.18</v>
+        <v>192.1799926757812</v>
       </c>
       <c r="E2462" t="n">
-        <v>194.26</v>
+        <v>194.2599945068359</v>
       </c>
       <c r="F2462" t="n">
         <v>829811</v>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B2463" t="n">
+        <v>191.51</v>
+      </c>
+      <c r="C2463" t="n">
+        <v>192.39</v>
+      </c>
+      <c r="D2463" t="n">
+        <v>189.8</v>
+      </c>
+      <c r="E2463" t="n">
+        <v>190</v>
+      </c>
+      <c r="F2463" t="n">
+        <v>323121</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2463"/>
+  <dimension ref="A1:F2464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49672,19 +49672,39 @@
         <v>46279</v>
       </c>
       <c r="B2463" t="n">
-        <v>191.51</v>
+        <v>191.5099945068359</v>
       </c>
       <c r="C2463" t="n">
-        <v>192.39</v>
+        <v>192.3899993896484</v>
       </c>
       <c r="D2463" t="n">
-        <v>189.8</v>
+        <v>189.8000030517578</v>
       </c>
       <c r="E2463" t="n">
         <v>190</v>
       </c>
       <c r="F2463" t="n">
         <v>323121</v>
+      </c>
+    </row>
+    <row r="2464">
+      <c r="A2464" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B2464" t="n">
+        <v>192.42</v>
+      </c>
+      <c r="C2464" t="n">
+        <v>193.81</v>
+      </c>
+      <c r="D2464" t="n">
+        <v>191.07</v>
+      </c>
+      <c r="E2464" t="n">
+        <v>192.56</v>
+      </c>
+      <c r="F2464" t="n">
+        <v>194054</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2464"/>
+  <dimension ref="A1:F2465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49692,19 +49692,39 @@
         <v>46280</v>
       </c>
       <c r="B2464" t="n">
-        <v>192.42</v>
+        <v>192.4199981689453</v>
       </c>
       <c r="C2464" t="n">
-        <v>193.81</v>
+        <v>193.8099975585938</v>
       </c>
       <c r="D2464" t="n">
-        <v>191.07</v>
+        <v>191.0700073242188</v>
       </c>
       <c r="E2464" t="n">
-        <v>192.56</v>
+        <v>192.5599975585938</v>
       </c>
       <c r="F2464" t="n">
         <v>194054</v>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B2465" t="n">
+        <v>191.45</v>
+      </c>
+      <c r="C2465" t="n">
+        <v>193</v>
+      </c>
+      <c r="D2465" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="E2465" t="n">
+        <v>192.42</v>
+      </c>
+      <c r="F2465" t="n">
+        <v>294313</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2465"/>
+  <dimension ref="A1:F2466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49712,19 +49712,39 @@
         <v>46281</v>
       </c>
       <c r="B2465" t="n">
-        <v>191.45</v>
+        <v>191.4499969482422</v>
       </c>
       <c r="C2465" t="n">
         <v>193</v>
       </c>
       <c r="D2465" t="n">
-        <v>190.9</v>
+        <v>190.8999938964844</v>
       </c>
       <c r="E2465" t="n">
-        <v>192.42</v>
+        <v>192.4199981689453</v>
       </c>
       <c r="F2465" t="n">
         <v>294313</v>
+      </c>
+    </row>
+    <row r="2466">
+      <c r="A2466" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B2466" t="n">
+        <v>192.19</v>
+      </c>
+      <c r="C2466" t="n">
+        <v>193.04</v>
+      </c>
+      <c r="D2466" t="n">
+        <v>188.95</v>
+      </c>
+      <c r="E2466" t="n">
+        <v>192.2</v>
+      </c>
+      <c r="F2466" t="n">
+        <v>342160</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2466"/>
+  <dimension ref="A1:F2467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49731,20 +49731,32 @@
       <c r="A2466" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B2466" t="n">
-        <v>192.19</v>
-      </c>
-      <c r="C2466" t="n">
-        <v>193.04</v>
-      </c>
-      <c r="D2466" t="n">
-        <v>188.95</v>
-      </c>
-      <c r="E2466" t="n">
-        <v>192.2</v>
-      </c>
+      <c r="B2466" t="inlineStr"/>
+      <c r="C2466" t="inlineStr"/>
+      <c r="D2466" t="inlineStr"/>
+      <c r="E2466" t="inlineStr"/>
       <c r="F2466" t="n">
-        <v>342160</v>
+        <v>195340</v>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="A2467" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B2467" t="n">
+        <v>191.41</v>
+      </c>
+      <c r="C2467" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="D2467" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="E2467" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="F2467" t="n">
+        <v>195831</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2467"/>
+  <dimension ref="A1:F2468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49731,12 +49731,20 @@
       <c r="A2466" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B2466" t="inlineStr"/>
-      <c r="C2466" t="inlineStr"/>
-      <c r="D2466" t="inlineStr"/>
-      <c r="E2466" t="inlineStr"/>
+      <c r="B2466" t="n">
+        <v>192.1900024414062</v>
+      </c>
+      <c r="C2466" t="n">
+        <v>193.0399932861328</v>
+      </c>
+      <c r="D2466" t="n">
+        <v>188.9700012207031</v>
+      </c>
+      <c r="E2466" t="n">
+        <v>192.1999969482422</v>
+      </c>
       <c r="F2466" t="n">
-        <v>195340</v>
+        <v>342160</v>
       </c>
     </row>
     <row r="2467">
@@ -49744,19 +49752,39 @@
         <v>46283</v>
       </c>
       <c r="B2467" t="n">
-        <v>191.41</v>
+        <v>191.4100036621094</v>
       </c>
       <c r="C2467" t="n">
-        <v>191.67</v>
+        <v>191.6699981689453</v>
       </c>
       <c r="D2467" t="n">
         <v>190.5</v>
       </c>
       <c r="E2467" t="n">
-        <v>191.2</v>
+        <v>191.1999969482422</v>
       </c>
       <c r="F2467" t="n">
         <v>195831</v>
+      </c>
+    </row>
+    <row r="2468">
+      <c r="A2468" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B2468" t="n">
+        <v>192.83</v>
+      </c>
+      <c r="C2468" t="n">
+        <v>193.64</v>
+      </c>
+      <c r="D2468" t="n">
+        <v>191.51</v>
+      </c>
+      <c r="E2468" t="n">
+        <v>192.45</v>
+      </c>
+      <c r="F2468" t="n">
+        <v>141561</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2468"/>
+  <dimension ref="A1:F2469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49772,19 +49772,39 @@
         <v>46286</v>
       </c>
       <c r="B2468" t="n">
-        <v>192.83</v>
+        <v>192.8300018310547</v>
       </c>
       <c r="C2468" t="n">
-        <v>193.64</v>
+        <v>193.6399993896484</v>
       </c>
       <c r="D2468" t="n">
-        <v>191.51</v>
+        <v>191.5099945068359</v>
       </c>
       <c r="E2468" t="n">
-        <v>192.45</v>
+        <v>192.4499969482422</v>
       </c>
       <c r="F2468" t="n">
         <v>141561</v>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="A2469" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B2469" t="n">
+        <v>193.6</v>
+      </c>
+      <c r="C2469" t="n">
+        <v>193.88</v>
+      </c>
+      <c r="D2469" t="n">
+        <v>191</v>
+      </c>
+      <c r="E2469" t="n">
+        <v>191.49</v>
+      </c>
+      <c r="F2469" t="n">
+        <v>332099</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2469"/>
+  <dimension ref="A1:F2470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49792,19 +49792,39 @@
         <v>46287</v>
       </c>
       <c r="B2469" t="n">
-        <v>193.6</v>
+        <v>193.6000061035156</v>
       </c>
       <c r="C2469" t="n">
-        <v>193.88</v>
+        <v>193.8800048828125</v>
       </c>
       <c r="D2469" t="n">
         <v>191</v>
       </c>
       <c r="E2469" t="n">
-        <v>191.49</v>
+        <v>191.4900054931641</v>
       </c>
       <c r="F2469" t="n">
         <v>332099</v>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="A2470" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B2470" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="C2470" t="n">
+        <v>194.9</v>
+      </c>
+      <c r="D2470" t="n">
+        <v>191.82</v>
+      </c>
+      <c r="E2470" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="F2470" t="n">
+        <v>248799</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2470"/>
+  <dimension ref="A1:F2471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49812,19 +49812,39 @@
         <v>46288</v>
       </c>
       <c r="B2470" t="n">
-        <v>191.9</v>
+        <v>191.8999938964844</v>
       </c>
       <c r="C2470" t="n">
-        <v>194.9</v>
+        <v>194.8999938964844</v>
       </c>
       <c r="D2470" t="n">
-        <v>191.82</v>
+        <v>191.8200073242188</v>
       </c>
       <c r="E2470" t="n">
-        <v>192.96</v>
+        <v>192.9600067138672</v>
       </c>
       <c r="F2470" t="n">
         <v>248799</v>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="A2471" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B2471" t="n">
+        <v>189.83</v>
+      </c>
+      <c r="C2471" t="n">
+        <v>192.31</v>
+      </c>
+      <c r="D2471" t="n">
+        <v>189.81</v>
+      </c>
+      <c r="E2471" t="n">
+        <v>192.07</v>
+      </c>
+      <c r="F2471" t="n">
+        <v>419641</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2471"/>
+  <dimension ref="A1:F2472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49832,19 +49832,39 @@
         <v>46289</v>
       </c>
       <c r="B2471" t="n">
-        <v>189.83</v>
+        <v>189.8300018310547</v>
       </c>
       <c r="C2471" t="n">
-        <v>192.31</v>
+        <v>192.3099975585938</v>
       </c>
       <c r="D2471" t="n">
-        <v>189.81</v>
+        <v>189.8099975585938</v>
       </c>
       <c r="E2471" t="n">
-        <v>192.07</v>
+        <v>192.0700073242188</v>
       </c>
       <c r="F2471" t="n">
         <v>419641</v>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B2472" t="n">
+        <v>189.68</v>
+      </c>
+      <c r="C2472" t="n">
+        <v>190.26</v>
+      </c>
+      <c r="D2472" t="n">
+        <v>188.15</v>
+      </c>
+      <c r="E2472" t="n">
+        <v>189.83</v>
+      </c>
+      <c r="F2472" t="n">
+        <v>374170</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2472"/>
+  <dimension ref="A1:F2473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49852,19 +49852,39 @@
         <v>46290</v>
       </c>
       <c r="B2472" t="n">
-        <v>189.68</v>
+        <v>189.6799926757812</v>
       </c>
       <c r="C2472" t="n">
-        <v>190.26</v>
+        <v>190.25</v>
       </c>
       <c r="D2472" t="n">
-        <v>188.15</v>
+        <v>188.1499938964844</v>
       </c>
       <c r="E2472" t="n">
-        <v>189.83</v>
+        <v>189.8300018310547</v>
       </c>
       <c r="F2472" t="n">
         <v>374170</v>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B2473" t="n">
+        <v>188.87</v>
+      </c>
+      <c r="C2473" t="n">
+        <v>190.09</v>
+      </c>
+      <c r="D2473" t="n">
+        <v>187.7</v>
+      </c>
+      <c r="E2473" t="n">
+        <v>189.24</v>
+      </c>
+      <c r="F2473" t="n">
+        <v>270714</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2473"/>
+  <dimension ref="A1:F2474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49872,19 +49872,39 @@
         <v>46293</v>
       </c>
       <c r="B2473" t="n">
-        <v>188.87</v>
+        <v>188.8699951171875</v>
       </c>
       <c r="C2473" t="n">
-        <v>190.09</v>
+        <v>190</v>
       </c>
       <c r="D2473" t="n">
-        <v>187.7</v>
+        <v>187.7400054931641</v>
       </c>
       <c r="E2473" t="n">
-        <v>189.24</v>
+        <v>189.2400054931641</v>
       </c>
       <c r="F2473" t="n">
         <v>270714</v>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B2474" t="n">
+        <v>189.73</v>
+      </c>
+      <c r="C2474" t="n">
+        <v>190.13</v>
+      </c>
+      <c r="D2474" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="E2474" t="n">
+        <v>188.48</v>
+      </c>
+      <c r="F2474" t="n">
+        <v>319578</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2474"/>
+  <dimension ref="A1:F2475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49892,19 +49892,39 @@
         <v>46294</v>
       </c>
       <c r="B2474" t="n">
-        <v>189.73</v>
+        <v>189.7299957275391</v>
       </c>
       <c r="C2474" t="n">
-        <v>190.13</v>
+        <v>190.1300048828125</v>
       </c>
       <c r="D2474" t="n">
         <v>187.5</v>
       </c>
       <c r="E2474" t="n">
-        <v>188.48</v>
+        <v>188.4799957275391</v>
       </c>
       <c r="F2474" t="n">
         <v>319578</v>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B2475" t="n">
+        <v>193.02</v>
+      </c>
+      <c r="C2475" t="n">
+        <v>194.18</v>
+      </c>
+      <c r="D2475" t="n">
+        <v>190.92</v>
+      </c>
+      <c r="E2475" t="n">
+        <v>192.38</v>
+      </c>
+      <c r="F2475" t="n">
+        <v>435047</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2475"/>
+  <dimension ref="A1:F2476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49912,19 +49912,39 @@
         <v>46295</v>
       </c>
       <c r="B2475" t="n">
-        <v>193.02</v>
+        <v>193.0200042724609</v>
       </c>
       <c r="C2475" t="n">
-        <v>194.18</v>
+        <v>194.1799926757812</v>
       </c>
       <c r="D2475" t="n">
-        <v>190.92</v>
+        <v>190.9199981689453</v>
       </c>
       <c r="E2475" t="n">
-        <v>192.38</v>
+        <v>192.3800048828125</v>
       </c>
       <c r="F2475" t="n">
         <v>435047</v>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2476" t="n">
+        <v>193.53</v>
+      </c>
+      <c r="C2476" t="n">
+        <v>193.67</v>
+      </c>
+      <c r="D2476" t="n">
+        <v>190.76</v>
+      </c>
+      <c r="E2476" t="n">
+        <v>193.35</v>
+      </c>
+      <c r="F2476" t="n">
+        <v>319095</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2476"/>
+  <dimension ref="A1:F2477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49932,19 +49932,39 @@
         <v>46296</v>
       </c>
       <c r="B2476" t="n">
-        <v>193.53</v>
+        <v>193.5500030517578</v>
       </c>
       <c r="C2476" t="n">
-        <v>193.67</v>
+        <v>194.1799926757812</v>
       </c>
       <c r="D2476" t="n">
-        <v>190.76</v>
+        <v>190.7599945068359</v>
       </c>
       <c r="E2476" t="n">
-        <v>193.35</v>
+        <v>192.3800048828125</v>
       </c>
       <c r="F2476" t="n">
         <v>319095</v>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B2477" t="n">
+        <v>198.87</v>
+      </c>
+      <c r="C2477" t="n">
+        <v>198.87</v>
+      </c>
+      <c r="D2477" t="n">
+        <v>192.3</v>
+      </c>
+      <c r="E2477" t="n">
+        <v>196.24</v>
+      </c>
+      <c r="F2477" t="n">
+        <v>446057</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2477"/>
+  <dimension ref="A1:F2478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49952,19 +49952,39 @@
         <v>46297</v>
       </c>
       <c r="B2477" t="n">
-        <v>198.87</v>
+        <v>198.8699951171875</v>
       </c>
       <c r="C2477" t="n">
-        <v>198.87</v>
+        <v>198.8699951171875</v>
       </c>
       <c r="D2477" t="n">
-        <v>192.3</v>
+        <v>192.3000030517578</v>
       </c>
       <c r="E2477" t="n">
-        <v>196.24</v>
+        <v>196.2400054931641</v>
       </c>
       <c r="F2477" t="n">
         <v>446057</v>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2478" t="n">
+        <v>214.19</v>
+      </c>
+      <c r="C2478" t="n">
+        <v>218</v>
+      </c>
+      <c r="D2478" t="n">
+        <v>212.35</v>
+      </c>
+      <c r="E2478" t="n">
+        <v>213.2</v>
+      </c>
+      <c r="F2478" t="n">
+        <v>1492805</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2478"/>
+  <dimension ref="A1:F2479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49972,19 +49972,39 @@
         <v>46300</v>
       </c>
       <c r="B2478" t="n">
-        <v>214.19</v>
+        <v>214.1900024414062</v>
       </c>
       <c r="C2478" t="n">
         <v>218</v>
       </c>
       <c r="D2478" t="n">
-        <v>212.35</v>
+        <v>212.3500061035156</v>
       </c>
       <c r="E2478" t="n">
-        <v>213.2</v>
+        <v>213.1999969482422</v>
       </c>
       <c r="F2478" t="n">
         <v>1492805</v>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2479" t="n">
+        <v>212.47</v>
+      </c>
+      <c r="C2479" t="n">
+        <v>216.65</v>
+      </c>
+      <c r="D2479" t="n">
+        <v>211.26</v>
+      </c>
+      <c r="E2479" t="n">
+        <v>214.65</v>
+      </c>
+      <c r="F2479" t="n">
+        <v>408362</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2479"/>
+  <dimension ref="A1:F2480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49992,19 +49992,39 @@
         <v>46301</v>
       </c>
       <c r="B2479" t="n">
-        <v>212.47</v>
+        <v>212.4700012207031</v>
       </c>
       <c r="C2479" t="n">
-        <v>216.65</v>
+        <v>216.6499938964844</v>
       </c>
       <c r="D2479" t="n">
-        <v>211.26</v>
+        <v>211.2599945068359</v>
       </c>
       <c r="E2479" t="n">
-        <v>214.65</v>
+        <v>214.6499938964844</v>
       </c>
       <c r="F2479" t="n">
         <v>408362</v>
+      </c>
+    </row>
+    <row r="2480">
+      <c r="A2480" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2480" t="n">
+        <v>211.3</v>
+      </c>
+      <c r="C2480" t="n">
+        <v>213.59</v>
+      </c>
+      <c r="D2480" t="n">
+        <v>211</v>
+      </c>
+      <c r="E2480" t="n">
+        <v>212.96</v>
+      </c>
+      <c r="F2480" t="n">
+        <v>150558</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2480"/>
+  <dimension ref="A1:F2481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50012,19 +50012,39 @@
         <v>46302</v>
       </c>
       <c r="B2480" t="n">
-        <v>211.3</v>
+        <v>211.3000030517578</v>
       </c>
       <c r="C2480" t="n">
-        <v>213.59</v>
+        <v>213.5899963378906</v>
       </c>
       <c r="D2480" t="n">
         <v>211</v>
       </c>
       <c r="E2480" t="n">
-        <v>212.96</v>
+        <v>212.9600067138672</v>
       </c>
       <c r="F2480" t="n">
         <v>150558</v>
+      </c>
+    </row>
+    <row r="2481">
+      <c r="A2481" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2481" t="n">
+        <v>212.96</v>
+      </c>
+      <c r="C2481" t="n">
+        <v>214.99</v>
+      </c>
+      <c r="D2481" t="n">
+        <v>210.92</v>
+      </c>
+      <c r="E2481" t="n">
+        <v>211.3</v>
+      </c>
+      <c r="F2481" t="n">
+        <v>531970</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2481"/>
+  <dimension ref="A1:F2482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50032,19 +50032,39 @@
         <v>46303</v>
       </c>
       <c r="B2481" t="n">
-        <v>212.96</v>
+        <v>212.9600067138672</v>
       </c>
       <c r="C2481" t="n">
-        <v>214.99</v>
+        <v>214.9700012207031</v>
       </c>
       <c r="D2481" t="n">
-        <v>210.92</v>
+        <v>210.9499969482422</v>
       </c>
       <c r="E2481" t="n">
-        <v>211.3</v>
+        <v>211.3000030517578</v>
       </c>
       <c r="F2481" t="n">
         <v>531970</v>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2482" t="n">
+        <v>216.1</v>
+      </c>
+      <c r="C2482" t="n">
+        <v>216.53</v>
+      </c>
+      <c r="D2482" t="n">
+        <v>214.32</v>
+      </c>
+      <c r="E2482" t="n">
+        <v>214.85</v>
+      </c>
+      <c r="F2482" t="n">
+        <v>473337</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -50052,16 +50052,16 @@
         <v>46304</v>
       </c>
       <c r="B2482" t="n">
-        <v>216.1</v>
+        <v>216.1000061035156</v>
       </c>
       <c r="C2482" t="n">
-        <v>216.53</v>
+        <v>216.5299987792969</v>
       </c>
       <c r="D2482" t="n">
-        <v>214.32</v>
+        <v>214.3399963378906</v>
       </c>
       <c r="E2482" t="n">
-        <v>214.85</v>
+        <v>214.8500061035156</v>
       </c>
       <c r="F2482" t="n">
         <v>473337</v>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2482"/>
+  <dimension ref="A1:F2483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50067,6 +50067,26 @@
         <v>473337</v>
       </c>
     </row>
+    <row r="2483">
+      <c r="A2483" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2483" t="n">
+        <v>213.55</v>
+      </c>
+      <c r="C2483" t="n">
+        <v>215.28</v>
+      </c>
+      <c r="D2483" t="n">
+        <v>212.6</v>
+      </c>
+      <c r="E2483" t="n">
+        <v>215.28</v>
+      </c>
+      <c r="F2483" t="n">
+        <v>938904</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2483"/>
+  <dimension ref="A1:F2484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50072,19 +50072,39 @@
         <v>46308</v>
       </c>
       <c r="B2483" t="n">
-        <v>213.55</v>
+        <v>213.5500030517578</v>
       </c>
       <c r="C2483" t="n">
-        <v>215.28</v>
+        <v>215.2799987792969</v>
       </c>
       <c r="D2483" t="n">
-        <v>212.6</v>
+        <v>212.6000061035156</v>
       </c>
       <c r="E2483" t="n">
-        <v>215.28</v>
+        <v>215.2799987792969</v>
       </c>
       <c r="F2483" t="n">
         <v>938904</v>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2484" t="n">
+        <v>213.44</v>
+      </c>
+      <c r="C2484" t="n">
+        <v>214.1</v>
+      </c>
+      <c r="D2484" t="n">
+        <v>209.95</v>
+      </c>
+      <c r="E2484" t="n">
+        <v>211.76</v>
+      </c>
+      <c r="F2484" t="n">
+        <v>444153</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2484"/>
+  <dimension ref="A1:F2485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50092,19 +50092,39 @@
         <v>46309</v>
       </c>
       <c r="B2484" t="n">
-        <v>213.44</v>
+        <v>213.4400024414062</v>
       </c>
       <c r="C2484" t="n">
-        <v>214.1</v>
+        <v>214.0800018310547</v>
       </c>
       <c r="D2484" t="n">
-        <v>209.95</v>
+        <v>209.9499969482422</v>
       </c>
       <c r="E2484" t="n">
-        <v>211.76</v>
+        <v>211.7599945068359</v>
       </c>
       <c r="F2484" t="n">
         <v>444153</v>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2485" t="n">
+        <v>211.24</v>
+      </c>
+      <c r="C2485" t="n">
+        <v>213.28</v>
+      </c>
+      <c r="D2485" t="n">
+        <v>210</v>
+      </c>
+      <c r="E2485" t="n">
+        <v>211.5</v>
+      </c>
+      <c r="F2485" t="n">
+        <v>395633</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2485"/>
+  <dimension ref="A1:F2486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50112,10 +50112,10 @@
         <v>46310</v>
       </c>
       <c r="B2485" t="n">
-        <v>211.24</v>
+        <v>211.2400054931641</v>
       </c>
       <c r="C2485" t="n">
-        <v>213.28</v>
+        <v>213.2700042724609</v>
       </c>
       <c r="D2485" t="n">
         <v>210</v>
@@ -50125,6 +50125,26 @@
       </c>
       <c r="F2485" t="n">
         <v>395633</v>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2486" t="n">
+        <v>212.38</v>
+      </c>
+      <c r="C2486" t="n">
+        <v>213.07</v>
+      </c>
+      <c r="D2486" t="n">
+        <v>210.98</v>
+      </c>
+      <c r="E2486" t="n">
+        <v>212.23</v>
+      </c>
+      <c r="F2486" t="n">
+        <v>374171</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2486"/>
+  <dimension ref="A1:F2487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50132,19 +50132,39 @@
         <v>46311</v>
       </c>
       <c r="B2486" t="n">
-        <v>212.38</v>
+        <v>212.3800048828125</v>
       </c>
       <c r="C2486" t="n">
-        <v>213.07</v>
+        <v>213.0700073242188</v>
       </c>
       <c r="D2486" t="n">
-        <v>210.98</v>
+        <v>210.9799957275391</v>
       </c>
       <c r="E2486" t="n">
-        <v>212.23</v>
+        <v>212.2299957275391</v>
       </c>
       <c r="F2486" t="n">
         <v>374171</v>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2487" t="n">
+        <v>212</v>
+      </c>
+      <c r="C2487" t="n">
+        <v>214.3</v>
+      </c>
+      <c r="D2487" t="n">
+        <v>211.03</v>
+      </c>
+      <c r="E2487" t="n">
+        <v>214.27</v>
+      </c>
+      <c r="F2487" t="n">
+        <v>340989</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2487"/>
+  <dimension ref="A1:F2488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50155,16 +50155,36 @@
         <v>212</v>
       </c>
       <c r="C2487" t="n">
-        <v>214.3</v>
+        <v>214.3000030517578</v>
       </c>
       <c r="D2487" t="n">
-        <v>211.03</v>
+        <v>211.0299987792969</v>
       </c>
       <c r="E2487" t="n">
-        <v>214.27</v>
+        <v>214.2700042724609</v>
       </c>
       <c r="F2487" t="n">
         <v>340989</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>215.28</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>215.86</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>213.42</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>214.42</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>478092</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2488"/>
+  <dimension ref="A1:F2489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50172,19 +50172,39 @@
         <v>46315</v>
       </c>
       <c r="B2488" t="n">
-        <v>215.28</v>
+        <v>215.2799987792969</v>
       </c>
       <c r="C2488" t="n">
-        <v>215.86</v>
+        <v>215.8600006103516</v>
       </c>
       <c r="D2488" t="n">
-        <v>213.42</v>
+        <v>213.4199981689453</v>
       </c>
       <c r="E2488" t="n">
-        <v>214.42</v>
+        <v>214.4199981689453</v>
       </c>
       <c r="F2488" t="n">
         <v>478092</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>213.45</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>216.96</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>212.67</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>216.96</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>689969</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2489"/>
+  <dimension ref="A1:F2490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50192,19 +50192,39 @@
         <v>46316</v>
       </c>
       <c r="B2489" t="n">
-        <v>213.45</v>
+        <v>213.4499969482422</v>
       </c>
       <c r="C2489" t="n">
-        <v>216.96</v>
+        <v>216.9600067138672</v>
       </c>
       <c r="D2489" t="n">
-        <v>212.67</v>
+        <v>212.6699981689453</v>
       </c>
       <c r="E2489" t="n">
-        <v>216.96</v>
+        <v>216.9600067138672</v>
       </c>
       <c r="F2489" t="n">
         <v>689969</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>210.99</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>212.88</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>209.77</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>823497</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2490"/>
+  <dimension ref="A1:F2491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50212,19 +50212,39 @@
         <v>46317</v>
       </c>
       <c r="B2490" t="n">
-        <v>210.99</v>
+        <v>210.9900054931641</v>
       </c>
       <c r="C2490" t="n">
-        <v>212.88</v>
+        <v>212.8800048828125</v>
       </c>
       <c r="D2490" t="n">
-        <v>209.77</v>
+        <v>209.7899932861328</v>
       </c>
       <c r="E2490" t="n">
         <v>212.5</v>
       </c>
       <c r="F2490" t="n">
         <v>823497</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>211.86</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>212.65</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>210.05</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>211.44</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>379549</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2491"/>
+  <dimension ref="A1:F2492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50232,19 +50232,39 @@
         <v>46318</v>
       </c>
       <c r="B2491" t="n">
-        <v>211.86</v>
+        <v>211.8600006103516</v>
       </c>
       <c r="C2491" t="n">
-        <v>212.65</v>
+        <v>212.6499938964844</v>
       </c>
       <c r="D2491" t="n">
-        <v>210.05</v>
+        <v>210.0500030517578</v>
       </c>
       <c r="E2491" t="n">
-        <v>211.44</v>
+        <v>211.4400024414062</v>
       </c>
       <c r="F2491" t="n">
         <v>379549</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>188.97</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>172.5</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>4580882</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2492"/>
+  <dimension ref="A1:F2493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50252,19 +50252,39 @@
         <v>46321</v>
       </c>
       <c r="B2492" t="n">
-        <v>182.3</v>
+        <v>182.3000030517578</v>
       </c>
       <c r="C2492" t="n">
-        <v>188.97</v>
+        <v>188.9700012207031</v>
       </c>
       <c r="D2492" t="n">
-        <v>172.5</v>
+        <v>118.5199966430664</v>
       </c>
       <c r="E2492" t="n">
-        <v>172.5</v>
+        <v>119.9599990844727</v>
       </c>
       <c r="F2492" t="n">
-        <v>4580882</v>
+        <v>4584594</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>180.67</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>1461216</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2493"/>
+  <dimension ref="A1:F2494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50272,19 +50272,39 @@
         <v>46322</v>
       </c>
       <c r="B2493" t="n">
-        <v>181.7</v>
+        <v>181.6999969482422</v>
       </c>
       <c r="C2493" t="n">
-        <v>184.7</v>
+        <v>184.6399993896484</v>
       </c>
       <c r="D2493" t="n">
-        <v>180.67</v>
+        <v>180.6900024414062</v>
       </c>
       <c r="E2493" t="n">
-        <v>183.8</v>
+        <v>183.8000030517578</v>
       </c>
       <c r="F2493" t="n">
         <v>1461216</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>176.83</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>175.52</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>181.25</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>932096</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2494"/>
+  <dimension ref="A1:F2495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50292,19 +50292,39 @@
         <v>46323</v>
       </c>
       <c r="B2494" t="n">
-        <v>176.83</v>
+        <v>176.8300018310547</v>
       </c>
       <c r="C2494" t="n">
         <v>181.25</v>
       </c>
       <c r="D2494" t="n">
-        <v>175.52</v>
+        <v>175.5200042724609</v>
       </c>
       <c r="E2494" t="n">
         <v>181.25</v>
       </c>
       <c r="F2494" t="n">
         <v>932096</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>177</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>174.29</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>177</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>1428859</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVV11.xlsx
+++ b/database/BOVV11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2495"/>
+  <dimension ref="A1:F2496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50318,13 +50318,33 @@
         <v>177</v>
       </c>
       <c r="D2495" t="n">
-        <v>174.29</v>
+        <v>174.2899932861328</v>
       </c>
       <c r="E2495" t="n">
         <v>177</v>
       </c>
       <c r="F2495" t="n">
         <v>1428859</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>173.7</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>174.69</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>172.3</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>173.12</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>1128729</v>
       </c>
     </row>
   </sheetData>
